--- a/ru/downloads/data-excel/9.b.1.xlsx
+++ b/ru/downloads/data-excel/9.b.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист" sheetId="1" r:id="rId1"/>
@@ -274,7 +274,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -309,6 +309,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -639,13 +642,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="51" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
@@ -666,7 +669,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -687,7 +690,7 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -702,7 +705,7 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>12</v>
       </c>
@@ -754,8 +757,11 @@
       <c r="Q4" s="2">
         <v>2023</v>
       </c>
+      <c r="R4" s="2">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q5" s="7">
         <v>3.2</v>
       </c>
+      <c r="R5" s="13">
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
